--- a/ClientExcel/Game/Music.xlsx
+++ b/ClientExcel/Game/Music.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>#</t>
   </si>
@@ -38,13 +38,7 @@
     <t>Id</t>
   </si>
   <si>
-    <t>AssetName</t>
-  </si>
-  <si>
     <t>AssetId</t>
-  </si>
-  <si>
-    <t>GroupName</t>
   </si>
   <si>
     <t>GroupId</t>
@@ -53,22 +47,16 @@
     <t>Int32</t>
   </si>
   <si>
-    <t>String</t>
-  </si>
-  <si>
     <t>音乐编号</t>
   </si>
   <si>
     <t>策划备注</t>
   </si>
   <si>
-    <t>资源名称</t>
+    <t>音乐编号枚举名</t>
   </si>
   <si>
     <t>资源编号</t>
-  </si>
-  <si>
-    <t>声音组名称</t>
   </si>
   <si>
     <t>声音组编号</t>
@@ -1025,10 +1013,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="16.875" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="16.875" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="16384" width="16.875" style="1" customWidth="1"/>
+    <col min="1" max="16383" width="16.875" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="16.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1039,67 +1028,54 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
